--- a/solar_lumped/docs/cost_correlation_data.xlsx
+++ b/solar_lumped/docs/cost_correlation_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/clara/github-repos/SAWH_TEAs/solar_lumped/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D272C9E-D964-CA42-9D21-898D96F9F846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614E200C-0A12-984E-8E52-CD786B52D858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{4A7AFC2F-903E-6E48-B14F-971F0335E139}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Name</t>
   </si>
@@ -50,7 +50,25 @@
     <t>Visual emissivity</t>
   </si>
   <si>
-    <t>Source</t>
+    <t>Spray paint</t>
+  </si>
+  <si>
+    <t>Tinox</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>1 square foot per oz to square meter per 200 mL, 0.5/0.628285101</t>
+  </si>
+  <si>
+    <t>Sources</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/FIBSHIELD-OEM-200ML-Graffiti-Multi-Color_1601288661459.html?spm=a2700.prosearch.normal_offer.d_title.1e6c67afL0YUo8&amp;priceId=66569374c6bf4937b3a646df2206a694, https://www.homedepot.com/p/Rust-Oleum-Painter-s-Touch-2X-12-oz-Flat-Black-General-Purpose-Spray-Paint-334020/307244849#see-more-details https://www.flir.com/discover/rd-science/use-low-cost-materials-to-increase-target-emissivity/</t>
+  </si>
+  <si>
+    <t>https://smmtmaterial.en.made-in-china.com/product/btpRqNzGJcWf/China-Blue-Selective-Coating-Tinox-High-Technology-for-Thermal-Collector-95-Absorptance.html?pv_id=1ju0k1qco063&amp;faw_id=1ju0k30df9b2&amp;bv_id=1ju0k30dhecc&amp;pbv_id=1ju0k1nti975s https://almecogroup.com/en/surface/tinox/</t>
   </si>
 </sst>
 </file>
@@ -422,10 +440,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8580865B-DE85-374F-A182-161F7C8512BB}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,7 +457,47 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.8</v>
+      </c>
+      <c r="C2">
+        <v>0.93</v>
+      </c>
+      <c r="D2">
+        <v>0.93</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>0.04</v>
+      </c>
+      <c r="D3">
+        <v>0.94</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
